--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/HRM/post DDV_HRM-2031-0180/Panel-28/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/HRM/post DDV_HRM-2031-0180/Panel-28/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.79126</v>
+        <v>16.9302</v>
       </c>
       <c r="D2" t="n">
-        <v>16.74731</v>
+        <v>16.53595</v>
       </c>
       <c r="E2" t="n">
-        <v>17.02804</v>
+        <v>16.82297</v>
       </c>
       <c r="F2" t="n">
-        <v>42.80448</v>
+        <v>42.83674</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05099</v>
+        <v>0.0512</v>
       </c>
       <c r="H2" t="n">
-        <v>1.82741</v>
+        <v>1.84513</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.23749</v>
+        <v>16.93239</v>
       </c>
       <c r="D3" t="n">
-        <v>16.74541</v>
+        <v>16.56485</v>
       </c>
       <c r="E3" t="n">
-        <v>17.05757</v>
+        <v>16.75548</v>
       </c>
       <c r="F3" t="n">
-        <v>43.01865</v>
+        <v>43.96642</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05071</v>
+        <v>0.05111</v>
       </c>
       <c r="H3" t="n">
-        <v>1.85717</v>
+        <v>1.84869</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.69357</v>
+        <v>17.08813</v>
       </c>
       <c r="D4" t="n">
-        <v>17.15565</v>
+        <v>16.69116</v>
       </c>
       <c r="E4" t="n">
-        <v>16.71458</v>
+        <v>16.97195</v>
       </c>
       <c r="F4" t="n">
-        <v>43.34891</v>
+        <v>42.90644</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05032</v>
+        <v>0.05222</v>
       </c>
       <c r="H4" t="n">
-        <v>1.85796</v>
+        <v>1.85566</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.58747</v>
+        <v>16.94973</v>
       </c>
       <c r="D6" t="n">
-        <v>16.18468</v>
+        <v>16.29317</v>
       </c>
       <c r="E6" t="n">
-        <v>16.46179</v>
+        <v>16.58979</v>
       </c>
       <c r="F6" t="n">
-        <v>22.12536</v>
+        <v>22.04815</v>
       </c>
       <c r="G6" t="n">
-        <v>34.50541</v>
+        <v>34.70935</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.70117</v>
+        <v>16.9352</v>
       </c>
       <c r="D7" t="n">
-        <v>15.99386</v>
+        <v>16.25611</v>
       </c>
       <c r="E7" t="n">
-        <v>16.54745</v>
+        <v>16.87989</v>
       </c>
       <c r="F7" t="n">
-        <v>21.61279</v>
+        <v>22.15318</v>
       </c>
       <c r="G7" t="n">
-        <v>33.79869</v>
+        <v>34.96931</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.55545</v>
+        <v>16.57399</v>
       </c>
       <c r="D8" t="n">
-        <v>16.23009</v>
+        <v>16.41047</v>
       </c>
       <c r="E8" t="n">
-        <v>16.42255</v>
+        <v>16.54177</v>
       </c>
       <c r="F8" t="n">
-        <v>22.34207</v>
+        <v>21.99726</v>
       </c>
       <c r="G8" t="n">
-        <v>34.10313</v>
+        <v>33.88556</v>
       </c>
     </row>
   </sheetData>
